--- a/data/2026-07/reporte_2026-07-31.xlsx
+++ b/data/2026-07/reporte_2026-07-31.xlsx
@@ -7,8 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💰 TGN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 Flujo Completo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Adjudicaciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📰 BORA Licitaciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💰 TGN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ Riesgo Licitatorio" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,53 +418,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>fecha_extraccion</t>
+          <t>fecha</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nro_proceso</t>
+          <t>organismo_contratante</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>nombre_proceso</t>
+          <t>tipo_proceso_bora</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>tipo_proceso</t>
+          <t>link_bora</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>fecha_apertura</t>
+          <t>proveedor_adjudicado</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>estado</t>
+          <t>cuit_proveedor</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>unidad_ejecutora</t>
+          <t>monto_adjudicado_bora</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>en_comprar</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>fuente</t>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nro_proceso_comprar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metodo_cruce_tgn</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
         </is>
       </c>
     </row>
@@ -472,42 +536,86 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46/20-0015-LPR26</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Servicio de reinstalación y ampliación del tendido de gas natural en Delegación Bariloche</t>
+          <t>Licitación Pública 04/26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Licitación Privada</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415305/20260731</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>31/07/2026 10:30 Hrs.</t>
+          <t>CONFECCIONES JOSÉ CONTARTESE Y CIA S.R.L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Publicado</t>
+          <t>30-52141731-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>46/20 - 20° Río Negro - DNV</t>
+          <t>$22.374.000,00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>✅ SÍ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Administración de Parques Nacionales</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>43.90238429</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>💰 ADJUDICADO + ORGANISMO CON PAGOS TGN</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>🔶 BORA + TGN (por organismo)</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
     </row>
@@ -519,42 +627,86 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84/19-0474-LPU26</t>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE VÍVERES SECOS POR 120 DÍAS CORRIDOS PARA EL COMANDO DE BRIGADA DE MONTAÑA VIII Y UU</t>
+          <t>Licitación Pública 22/2026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415306/20260731</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31/07/2026 10:30 Hrs.</t>
+          <t>MERCOSUR SEGURIDAD S.R.L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Publicado</t>
+          <t>30-71070541-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>84/19 - Comando Brigada de Montaña VIII</t>
+          <t>$170.820.000,00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>✅ SÍ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Administración de Parques Nacionales</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>43.90238429</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>💰 ADJUDICADO + ORGANISMO CON PAGOS TGN</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>🔶 BORA + TGN (por organismo)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
     </row>
@@ -566,465 +718,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84/19-0470-LPU26</t>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE PROD FRESCOS POR 120 DIAS CORRIDOS PARA EL COMANDO DE BRIGADA DE MONTAÑA VIII Y UU</t>
+          <t>Licitación Pública PROCESO COMPR.AR 63-0082-LPU25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>31/07/2026 10:45 Hrs.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>84/19 - Comando Brigada de Montaña VIII</t>
-        </is>
-      </c>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415307/20260731</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>46-0101-CDI26</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Puesta en marcha y mantenimiento de ascensores del Puente N. Avellaneda</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>31/07/2026 11:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>46/000 - Coordinación de Licitaciones y Contrataciones - DNV</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>47-0014-LPR26</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Alquiler equipos multifunción</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>31/07/2026 11:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>68-0065-CDI26</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN, DESINSTALACIÓN E INSTALACIÓN DE AIRES ACONDICIONADOS - INE "DR. JUAN H. JARA"</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>31/07/2026 11:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>80-0078-CDI26</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Adquisición del medicamento ABEMACICLIB 50 MG, 100 MG y 150 MG con logística incluida</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Contratación Directa</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>31/07/2026 11:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>80/000 - Dirección General de Administración - MS</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>84/147-1020-LPR26</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Adquisición de Repuestos Informáticos para la escuela militar de monte</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Licitación Privada</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>31/07/2026 11:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>84/147 - ESCUELA MILITAR DE MONTE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>84/28-0509-LPU26</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE PRODUCTOS CARNICOS PARA 120 DIAS (OCT26/ENE27) - AGR AA EJ 601 – EC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>31/07/2026 11:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>84/28 - Jefatura Agrupación Artillería Antiaérea Ej. 601 - EC</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>80-0038-LPU26</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Adquisicion de Medicamentos del Programa Nacional de Seguimiento Postrasplante</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Licitación Pública</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>31/07/2026 11:00 Hrs.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>80/000 - Dirección General de Administración - MS</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12345678910...</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Comprar.gob.ar</t>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>✅ SÍ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Administración Nacional de Aviación Civil</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>3366.71186018</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>🔶 BORA + TGN (por organismo)</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
         </is>
       </c>
     </row>
@@ -1039,6 +800,2961 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_muestra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/26</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2415305</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415305/20260731</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CONFECCIONES JOSÉ CONTARTESE Y CIA S.R.L</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30-52141731-1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$22.374.000,00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/b3JqdlBNaXVoVVJSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA CUYO
+Licitación Pública 04/26
+Expediente  Nº:  EX-2026-02324707-  -ARCA-SECFDVAFCU#SDGOAI  Objeto  de  la  contratación:
+Adquisición  de  indumenta</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 22/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2415306</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415306/20260731</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MERCOSUR SEGURIDAD S.R.L</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30-71070541-7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>$170.820.000,00</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/eVJmRkpwajRFUVJSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA HIDROVÍA
+Licitación Pública 22/2026
+Ejercicio:  2026  Expediente  Nº:  EX-2026-01254739--ARCA-SECFDVAFHI#SDGOAI  Objeto  de  la
+contratación: “SERV</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPR.AR 63-0082-LPU25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2415307</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415307/20260731</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/RFgyeDhMMDdYbTlSbkVWUVVZR3c4dz09
+ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL
+Licitación Pública PROCESO COMPR.AR 63-0082-LPU25
+Clase/Causal del procedimiento: Etapa Única Nacional Modalidad: Sin modalidad N° de Expediente
+Electrónico: EX-2025-110738</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>es_adjudicacion</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SANIDAD Y CALIDAD AGROALIMENTARIA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0028/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2415261</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415261/20260731</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PREFECTURA NAVAL ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0031/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2415262</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415262/20260731</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0274/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2415263</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415263/20260731</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0480/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2415264</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415264/20260731</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0542/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2415265</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415265/20260731</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 108/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2415266</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415266/20260731</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA MATANZA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Licitación Pública de Etapa Única Nacional 18/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2415267</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415267/20260731</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0415/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2415268</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415268/20260731</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0416/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2415269</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415269/20260731</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0417/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2415270</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415270/20260731</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0418/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2415271</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415271/20260731</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0419/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2415272</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415272/20260731</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0475/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2415273</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415273/20260731</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0476/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2415274</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415274/20260731</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0477/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2415275</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415275/20260731</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0478/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2415276</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415276/20260731</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0479/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2415277</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415277/20260731</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0481/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2415278</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415278/20260731</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0491/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2415279</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415279/20260731</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA PLATA - SECRETARÍA DE PLANEAMIENTO, OBRAS Y SERVICIOS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Licitación Pública 07/26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2415280</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415280/20260731</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Licitación Pública 23/2026 Obra Pública</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2415281</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415281/20260731</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Licitación Pública 01/2026 DOSC-DCU</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OBRAS - VIALES</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2415282</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415282/20260731</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN NACIONAL DE VIALIDAD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Licitación Pública 14/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>OBRAS - VIALES</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2415283</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415283/20260731</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL RÍO CUARTO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Licitación Pública 05/26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2415284</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415284/20260731</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DEFENSORÍA DEL PUEBLO DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Licitación Pública 1/26</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2415285</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415285/20260731</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE DEFENSA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0005/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SERVICIOS - REFRIGERACION Y CALEFACCION</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2415286</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415286/20260731</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE SERVICIOS SOCIALES PARA JUBILADOS Y PENSIONADOS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Licitación Pública 15/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SERVICIOS - REFRIGERIOS, COMEDORES, LUNCH, COMIDAS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2415287</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415287/20260731</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ENERGÍA ARGENTINA S.A.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional FIN-SEG 01/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SEGUROS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2415288</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415288/20260731</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ENERGÍA ARGENTINA S.A.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional FIN-SEG 03/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SEGUROS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2415289</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415289/20260731</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE JUSTICIA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0002/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2415290</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415290/20260731</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JEFATURA DE GABINETE DE MINISTROS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0004/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2415291</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415291/20260731</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0006/2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2415292</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415292/20260731</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN NACIONAL DEL REGISTRO NACIONAL DE LAS PERSONAS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0006/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2415293</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415293/20260731</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0121/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2415294</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415294/20260731</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CORTE SUPREMA DE JUSTICIA DE LA NACIÓN - OBRA SOCIAL DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Licitación Pública 03/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2415295</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415295/20260731</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE JUSTICIA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Compulsa de precios 03/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2415296</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415296/20260731</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CORTE SUPREMA DE JUSTICIA DE LA NACIÓN - OBRA SOCIAL DEL PODER JUDICIAL DE LA NACION</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2415297</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415297/20260731</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL NORTE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Licitación Pública 10/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2415298</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415298/20260731</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>COMISIÓN ARBITRAL CONVENIO MULTILATERAL DEL 18.8.77</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Concursos de Precios 6/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2415299</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415299/20260731</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FABRICACIONES MILITARES SOCIEDAD ANÓNIMA UNIPERSONAL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Licitación Pública LPU-2026-SC-027</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2415300</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415300/20260731</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Licitación Pública 3/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - CONCESIONES</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2415301</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415301/20260731</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Subasta Pública 392-0048-SPU26</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - VARIOS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2415302</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415302/20260731</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Licitación Pública 24/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LOCACIONES - INMUEBLES (LOC)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2415303</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415303/20260731</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA  - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Licitación Pública 25/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LOCACIONES - VARIOS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2415304</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415304/20260731</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA RÍO COLORADO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Licitación Pública 13/26</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DICTAMEN DE EVALUACION - DICTAMEN DE EVALUACION</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2415308</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415308/20260731</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nro_proceso</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>nombre_proceso</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fecha_apertura</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unidad_ejecutora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>46/20-0015-LPR26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Servicio de reinstalación y ampliación del tendido de gas natural en Delegación Bariloche</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>31/07/2026 10:30 Hrs.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>46/20 - 20° Río Negro - DNV</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>84/19-0474-LPU26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE VÍVERES SECOS POR 120 DÍAS CORRIDOS PARA EL COMANDO DE BRIGADA DE MONTAÑA VIII Y UU</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31/07/2026 10:30 Hrs.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>84/19 - Comando Brigada de Montaña VIII</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>84/19-0470-LPU26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE PROD FRESCOS POR 120 DIAS CORRIDOS PARA EL COMANDO DE BRIGADA DE MONTAÑA VIII Y UU</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31/07/2026 10:45 Hrs.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>84/19 - Comando Brigada de Montaña VIII</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>46-0101-CDI26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Puesta en marcha y mantenimiento de ascensores del Puente N. Avellaneda</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>31/07/2026 11:00 Hrs.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>46/000 - Coordinación de Licitaciones y Contrataciones - DNV</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>47-0014-LPR26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Alquiler equipos multifunción</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31/07/2026 11:00 Hrs.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>68-0065-CDI26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN, DESINSTALACIÓN E INSTALACIÓN DE AIRES ACONDICIONADOS - INE "DR. JUAN H. JARA"</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>31/07/2026 11:00 Hrs.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>80-0078-CDI26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Adquisición del medicamento ABEMACICLIB 50 MG, 100 MG y 150 MG con logística incluida</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Contratación Directa</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>31/07/2026 11:00 Hrs.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>80/000 - Dirección General de Administración - MS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>84/147-1020-LPR26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Adquisición de Repuestos Informáticos para la escuela militar de monte</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Licitación Privada</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>31/07/2026 11:00 Hrs.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>84/147 - ESCUELA MILITAR DE MONTE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>84/28-0509-LPU26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE PRODUCTOS CARNICOS PARA 120 DIAS (OCT26/ENE27) - AGR AA EJ 601 – EC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>31/07/2026 11:00 Hrs.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>84/28 - Jefatura Agrupación Artillería Antiaérea Ej. 601 - EC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>80-0038-LPU26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Adquisicion de Medicamentos del Programa Nacional de Seguimiento Postrasplante</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Licitación Pública</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>31/07/2026 11:00 Hrs.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Publicado</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>80/000 - Dirección General de Administración - MS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12345678910...</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://comprar.gob.ar/Compras.aspx?qs=W1HXHGHtH10=</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Comprar.gob.ar</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -23693,4 +26409,246 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/26</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30-52141731-1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>$22.374.000,00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>💰 ADJUDICADO + ORGANISMO CON PAGOS TGN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>🔶 BORA + TGN (por organismo)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415305/20260731</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA HIDROVÍA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 22/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30-71070541-7</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>$170.820.000,00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>💰 ADJUDICADO + ORGANISMO CON PAGOS TGN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>🔶 BORA + TGN (por organismo)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415306/20260731</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN NACIONAL DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Licitación Pública PROCESO COMPR.AR 63-0082-LPU25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>🔶 BORA + TGN (por organismo)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2415307/20260731</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>